--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3841,6 +3841,1503 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128344547</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>463836</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6717820</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128345047</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92661</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>463935</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6718037</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128344951</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>464004</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6718005</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128344588</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>463808</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6717789</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128344607</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92637</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>463843</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6717828</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128344377</v>
+      </c>
+      <c r="B36" t="n">
+        <v>88720</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>816</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Smultronkantarell</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Aphroditeola olida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>463733</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6717879</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128344472</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>463788</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6717928</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128344568</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>463797</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6717757</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128344428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>463779</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6717945</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128344397</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92661</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>463726</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6717875</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128344443</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>463788</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6717934</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128344890</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>463864</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6718020</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128344931</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>463919</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6718013</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128344834</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>463871</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6718029</v>
+      </c>
+      <c r="S44" t="n">
+        <v>50</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5338,6 +5338,220 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128403630</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kroktjärnarna O, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>463833</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6717817</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128403716</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92664</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kroktjärnarna O, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>463833</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6717817</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128344547</v>
+        <v>128345047</v>
       </c>
       <c r="B31" t="n">
-        <v>91375</v>
+        <v>92666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,26 +3854,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463836</v>
+        <v>463935</v>
       </c>
       <c r="R31" t="n">
-        <v>6717820</v>
+        <v>6718037</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128345047</v>
+        <v>128344547</v>
       </c>
       <c r="B32" t="n">
-        <v>92661</v>
+        <v>91380</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,26 +3959,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463935</v>
+        <v>463836</v>
       </c>
       <c r="R32" t="n">
-        <v>6718037</v>
+        <v>6717820</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128344951</v>
       </c>
       <c r="B33" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344588</v>
+        <v>128344607</v>
       </c>
       <c r="B34" t="n">
-        <v>79031</v>
+        <v>92642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,24 +4174,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463808</v>
+        <v>463843</v>
       </c>
       <c r="R34" t="n">
-        <v>6717789</v>
+        <v>6717828</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4264,10 +4268,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344607</v>
+        <v>128344588</v>
       </c>
       <c r="B35" t="n">
-        <v>92637</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,28 +4279,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463843</v>
+        <v>463808</v>
       </c>
       <c r="R35" t="n">
-        <v>6717828</v>
+        <v>6717789</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4372,7 +4372,7 @@
         <v>128344377</v>
       </c>
       <c r="B36" t="n">
-        <v>88720</v>
+        <v>88667</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>128344472</v>
       </c>
       <c r="B37" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,41 +4584,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128344568</v>
+        <v>128344428</v>
       </c>
       <c r="B38" t="n">
-        <v>91375</v>
+        <v>98478</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4626,13 +4627,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463797</v>
+        <v>463779</v>
       </c>
       <c r="R38" t="n">
-        <v>6717757</v>
+        <v>6717945</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,42 +4690,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128344428</v>
+        <v>128344568</v>
       </c>
       <c r="B39" t="n">
-        <v>98473</v>
+        <v>91380</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463779</v>
+        <v>463797</v>
       </c>
       <c r="R39" t="n">
-        <v>6717945</v>
+        <v>6717757</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>128344397</v>
       </c>
       <c r="B40" t="n">
-        <v>92661</v>
+        <v>92666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>128344443</v>
       </c>
       <c r="B41" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128344890</v>
       </c>
       <c r="B42" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,10 +5120,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128344931</v>
+        <v>128344834</v>
       </c>
       <c r="B43" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463919</v>
+        <v>463871</v>
       </c>
       <c r="R43" t="n">
-        <v>6718013</v>
+        <v>6718029</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5230,10 +5230,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128344834</v>
+        <v>128344931</v>
       </c>
       <c r="B44" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463871</v>
+        <v>463919</v>
       </c>
       <c r="R44" t="n">
-        <v>6718029</v>
+        <v>6718013</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5343,7 +5343,7 @@
         <v>128403630</v>
       </c>
       <c r="B45" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128403716</v>
       </c>
       <c r="B46" t="n">
-        <v>92664</v>
+        <v>92666</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3846,7 +3846,7 @@
         <v>128345047</v>
       </c>
       <c r="B31" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>128344547</v>
       </c>
       <c r="B32" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128344951</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>128344607</v>
       </c>
       <c r="B34" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128344588</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128344377</v>
       </c>
       <c r="B36" t="n">
-        <v>88667</v>
+        <v>88759</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>128344472</v>
       </c>
       <c r="B37" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>128344428</v>
       </c>
       <c r="B38" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>128344568</v>
       </c>
       <c r="B39" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>128344397</v>
       </c>
       <c r="B40" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>128344443</v>
       </c>
       <c r="B41" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128344890</v>
       </c>
       <c r="B42" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128344834</v>
       </c>
       <c r="B43" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>128344931</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128403630</v>
       </c>
       <c r="B45" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128403716</v>
       </c>
       <c r="B46" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -4163,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344607</v>
+        <v>128344588</v>
       </c>
       <c r="B34" t="n">
-        <v>92734</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,28 +4174,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4205,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463843</v>
+        <v>463808</v>
       </c>
       <c r="R34" t="n">
-        <v>6717828</v>
+        <v>6717789</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4268,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344588</v>
+        <v>128344607</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>92734</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4279,24 +4275,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463808</v>
+        <v>463843</v>
       </c>
       <c r="R35" t="n">
-        <v>6717789</v>
+        <v>6717828</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4584,42 +4584,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128344428</v>
+        <v>128344568</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>91472</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4627,13 +4626,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463779</v>
+        <v>463797</v>
       </c>
       <c r="R38" t="n">
-        <v>6717945</v>
+        <v>6717757</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4690,41 +4689,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128344568</v>
+        <v>128344428</v>
       </c>
       <c r="B39" t="n">
-        <v>91472</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463797</v>
+        <v>463779</v>
       </c>
       <c r="R39" t="n">
-        <v>6717757</v>
+        <v>6717945</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128345047</v>
+        <v>128344547</v>
       </c>
       <c r="B31" t="n">
-        <v>92758</v>
+        <v>91472</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,26 +3854,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463935</v>
+        <v>463836</v>
       </c>
       <c r="R31" t="n">
-        <v>6718037</v>
+        <v>6717820</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128344547</v>
+        <v>128345047</v>
       </c>
       <c r="B32" t="n">
-        <v>91472</v>
+        <v>92758</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,26 +3959,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463836</v>
+        <v>463935</v>
       </c>
       <c r="R32" t="n">
-        <v>6717820</v>
+        <v>6718037</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344588</v>
+        <v>128344607</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>92734</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,24 +4174,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463808</v>
+        <v>463843</v>
       </c>
       <c r="R34" t="n">
-        <v>6717789</v>
+        <v>6717828</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4264,10 +4268,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344607</v>
+        <v>128344588</v>
       </c>
       <c r="B35" t="n">
-        <v>92734</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,28 +4279,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463843</v>
+        <v>463808</v>
       </c>
       <c r="R35" t="n">
-        <v>6717828</v>
+        <v>6717789</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4584,41 +4584,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128344568</v>
+        <v>128344428</v>
       </c>
       <c r="B38" t="n">
-        <v>91472</v>
+        <v>98571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4626,13 +4627,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463797</v>
+        <v>463779</v>
       </c>
       <c r="R38" t="n">
-        <v>6717757</v>
+        <v>6717945</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,42 +4690,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128344428</v>
+        <v>128344568</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>91472</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463779</v>
+        <v>463797</v>
       </c>
       <c r="R39" t="n">
-        <v>6717945</v>
+        <v>6717757</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -4584,42 +4584,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128344428</v>
+        <v>128344568</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>91472</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4627,13 +4626,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463779</v>
+        <v>463797</v>
       </c>
       <c r="R38" t="n">
-        <v>6717945</v>
+        <v>6717757</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4690,41 +4689,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128344568</v>
+        <v>128344428</v>
       </c>
       <c r="B39" t="n">
-        <v>91472</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463797</v>
+        <v>463779</v>
       </c>
       <c r="R39" t="n">
-        <v>6717757</v>
+        <v>6717945</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128344547</v>
+        <v>128345047</v>
       </c>
       <c r="B31" t="n">
-        <v>91472</v>
+        <v>92770</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,26 +3854,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463836</v>
+        <v>463935</v>
       </c>
       <c r="R31" t="n">
-        <v>6717820</v>
+        <v>6718037</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128345047</v>
+        <v>128344547</v>
       </c>
       <c r="B32" t="n">
-        <v>92758</v>
+        <v>91484</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,26 +3959,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463935</v>
+        <v>463836</v>
       </c>
       <c r="R32" t="n">
-        <v>6718037</v>
+        <v>6717820</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128344951</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>128344607</v>
       </c>
       <c r="B34" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128344588</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128344377</v>
       </c>
       <c r="B36" t="n">
-        <v>88759</v>
+        <v>88771</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>128344472</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>128344568</v>
       </c>
       <c r="B38" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128344428</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>128344397</v>
       </c>
       <c r="B40" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>128344443</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128344890</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128344834</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>128344931</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128403630</v>
       </c>
       <c r="B45" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128403716</v>
       </c>
       <c r="B46" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128345047</v>
+        <v>128344547</v>
       </c>
       <c r="B31" t="n">
-        <v>92770</v>
+        <v>91486</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,26 +3854,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463935</v>
+        <v>463836</v>
       </c>
       <c r="R31" t="n">
-        <v>6718037</v>
+        <v>6717820</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128344547</v>
+        <v>128345047</v>
       </c>
       <c r="B32" t="n">
-        <v>91484</v>
+        <v>92772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,26 +3959,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463836</v>
+        <v>463935</v>
       </c>
       <c r="R32" t="n">
-        <v>6717820</v>
+        <v>6718037</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128344951</v>
       </c>
       <c r="B33" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>128344607</v>
       </c>
       <c r="B34" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128344588</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128344377</v>
       </c>
       <c r="B36" t="n">
-        <v>88771</v>
+        <v>88773</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>128344472</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>128344568</v>
       </c>
       <c r="B38" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128344428</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>128344397</v>
       </c>
       <c r="B40" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>128344443</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128344890</v>
       </c>
       <c r="B42" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128344834</v>
       </c>
       <c r="B43" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>128344931</v>
       </c>
       <c r="B44" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128403630</v>
       </c>
       <c r="B45" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128403716</v>
       </c>
       <c r="B46" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -4056,7 +4056,7 @@
         <v>128344951</v>
       </c>
       <c r="B33" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344607</v>
+        <v>128344588</v>
       </c>
       <c r="B34" t="n">
-        <v>92748</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,28 +4174,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4205,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463843</v>
+        <v>463808</v>
       </c>
       <c r="R34" t="n">
-        <v>6717828</v>
+        <v>6717789</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4268,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344588</v>
+        <v>128344607</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>92748</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4279,24 +4275,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463808</v>
+        <v>463843</v>
       </c>
       <c r="R35" t="n">
-        <v>6717789</v>
+        <v>6717828</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>128344472</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128344428</v>
       </c>
       <c r="B39" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>128344443</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128344890</v>
       </c>
       <c r="B42" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128344834</v>
       </c>
       <c r="B43" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>128344931</v>
       </c>
       <c r="B44" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3846,7 +3846,7 @@
         <v>128344547</v>
       </c>
       <c r="B31" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>128345047</v>
       </c>
       <c r="B32" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128344951</v>
       </c>
       <c r="B33" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344588</v>
+        <v>128344607</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>92749</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,24 +4174,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463808</v>
+        <v>463843</v>
       </c>
       <c r="R34" t="n">
-        <v>6717789</v>
+        <v>6717828</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4264,10 +4268,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344607</v>
+        <v>128344588</v>
       </c>
       <c r="B35" t="n">
-        <v>92748</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,28 +4279,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463843</v>
+        <v>463808</v>
       </c>
       <c r="R35" t="n">
-        <v>6717828</v>
+        <v>6717789</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>128344472</v>
       </c>
       <c r="B37" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>128344568</v>
       </c>
       <c r="B38" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128344428</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>128344397</v>
       </c>
       <c r="B40" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>128344443</v>
       </c>
       <c r="B41" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128344890</v>
       </c>
       <c r="B42" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128344834</v>
       </c>
       <c r="B43" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>128344931</v>
       </c>
       <c r="B44" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128403630</v>
       </c>
       <c r="B45" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128403716</v>
       </c>
       <c r="B46" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128344547</v>
+        <v>128345047</v>
       </c>
       <c r="B31" t="n">
-        <v>91487</v>
+        <v>92773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,26 +3854,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463836</v>
+        <v>463935</v>
       </c>
       <c r="R31" t="n">
-        <v>6717820</v>
+        <v>6718037</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128345047</v>
+        <v>128344547</v>
       </c>
       <c r="B32" t="n">
-        <v>92773</v>
+        <v>91487</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,26 +3959,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463935</v>
+        <v>463836</v>
       </c>
       <c r="R32" t="n">
-        <v>6718037</v>
+        <v>6717820</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344607</v>
+        <v>128344588</v>
       </c>
       <c r="B34" t="n">
-        <v>92749</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,28 +4174,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4205,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463843</v>
+        <v>463808</v>
       </c>
       <c r="R34" t="n">
-        <v>6717828</v>
+        <v>6717789</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4268,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344588</v>
+        <v>128344607</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>92749</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4279,24 +4275,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463808</v>
+        <v>463843</v>
       </c>
       <c r="R35" t="n">
-        <v>6717789</v>
+        <v>6717828</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4584,41 +4584,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128344568</v>
+        <v>128344428</v>
       </c>
       <c r="B38" t="n">
-        <v>91487</v>
+        <v>98592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4626,13 +4627,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463797</v>
+        <v>463779</v>
       </c>
       <c r="R38" t="n">
-        <v>6717757</v>
+        <v>6717945</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,42 +4690,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128344428</v>
+        <v>128344568</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>91487</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463779</v>
+        <v>463797</v>
       </c>
       <c r="R39" t="n">
-        <v>6717945</v>
+        <v>6717757</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>

--- a/artfynd/A 38410-2025 artfynd.xlsx
+++ b/artfynd/A 38410-2025 artfynd.xlsx
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128345047</v>
+        <v>128344547</v>
       </c>
       <c r="B31" t="n">
-        <v>92773</v>
+        <v>91514</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,26 +3854,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463935</v>
+        <v>463836</v>
       </c>
       <c r="R31" t="n">
-        <v>6718037</v>
+        <v>6717820</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128344547</v>
+        <v>128345047</v>
       </c>
       <c r="B32" t="n">
-        <v>91487</v>
+        <v>92800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,26 +3959,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463836</v>
+        <v>463935</v>
       </c>
       <c r="R32" t="n">
-        <v>6717820</v>
+        <v>6718037</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128344951</v>
       </c>
       <c r="B33" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344588</v>
+        <v>128344607</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>92776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,24 +4174,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463808</v>
+        <v>463843</v>
       </c>
       <c r="R34" t="n">
-        <v>6717789</v>
+        <v>6717828</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4264,10 +4268,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344607</v>
+        <v>128344588</v>
       </c>
       <c r="B35" t="n">
-        <v>92749</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,28 +4279,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463843</v>
+        <v>463808</v>
       </c>
       <c r="R35" t="n">
-        <v>6717828</v>
+        <v>6717789</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4372,7 +4372,7 @@
         <v>128344377</v>
       </c>
       <c r="B36" t="n">
-        <v>88773</v>
+        <v>88800</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>128344472</v>
       </c>
       <c r="B37" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>128344428</v>
       </c>
       <c r="B38" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>128344568</v>
       </c>
       <c r="B39" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>128344397</v>
       </c>
       <c r="B40" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>128344443</v>
       </c>
       <c r="B41" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128344890</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128344834</v>
       </c>
       <c r="B43" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>128344931</v>
       </c>
       <c r="B44" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>128403630</v>
       </c>
       <c r="B45" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>128403716</v>
       </c>
       <c r="B46" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
